--- a/PDF/data/experiencia_laboral_docente.xlsx
+++ b/PDF/data/experiencia_laboral_docente.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="73">
   <si>
     <t xml:space="preserve">what</t>
   </si>
@@ -37,16 +37,28 @@
     <t xml:space="preserve">why</t>
   </si>
   <si>
+    <t xml:space="preserve">Docente Investigadora – Facultad de Psicología</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidad El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bogotá, Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profesora Asociada</t>
+  </si>
+  <si>
     <t xml:space="preserve">Posdoctorado</t>
   </si>
   <si>
-    <t xml:space="preserve">Desde 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asociación Red de Mujeres Víctimas y Profesionales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bogotá, Colombia</t>
+    <t xml:space="preserve">2023 – 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asociación Red de Mujeres Víctimas y Profesionales – Minciencias</t>
   </si>
   <si>
     <t xml:space="preserve">\textbf{Proyecto: } La necesidad de generar procesos de reparación social a las mujeres víctimas y sobrevivientes de violencias sexuales en el marco del conflicto armado desde el quehacer periodístico. Diversas propuestas de tratamiento según contextos</t>
@@ -236,7 +248,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +270,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -302,8 +322,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -496,323 +524,340 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="87.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="85.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="87.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="85.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E4" s="0" t="s">
-        <v>11</v>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="0" t="s">
-        <v>17</v>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="0" t="s">
-        <v>18</v>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
-        <v>19</v>
+      <c r="E9" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="0" t="s">
-        <v>20</v>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="0" t="s">
-        <v>21</v>
+      <c r="E11" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="0" t="s">
-        <v>22</v>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="0" t="s">
-        <v>23</v>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="0" t="s">
-        <v>29</v>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="0" t="s">
-        <v>30</v>
+      <c r="E17" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="0" t="s">
-        <v>31</v>
+      <c r="E18" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="0" t="s">
-        <v>38</v>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="E24" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="0" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="0" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="0" t="s">
-        <v>68</v>
+      <c r="E33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/PDF/data/experiencia_laboral_docente.xlsx
+++ b/PDF/data/experiencia_laboral_docente.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Bogotá, Colombia</t>
   </si>
   <si>
-    <t xml:space="preserve">Profesora Asociada</t>
+    <t xml:space="preserve">Profesora Asociada, Facultad de Psicología y Centro de Diversidad, Equidad e Inclusión</t>
   </si>
   <si>
     <t xml:space="preserve">Posdoctorado</t>
@@ -525,7 +525,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="87.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.67"/>
